--- a/data/trans_orig/Q5411-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5411-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar el baño o ducha en 2007</t>
+          <t>Población según si es capaz de usar el baño o ducha en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6265</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18709</t>
+          <t>18658</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7951</t>
+          <t>7672</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22474</t>
+          <t>23685</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16141</t>
+          <t>16923</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35734</t>
+          <t>37802</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>14,29%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>96280</t>
+          <t>96331</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>108724</t>
+          <t>108560</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>127061</t>
+          <t>125850</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>141584</t>
+          <t>141863</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>228790</t>
+          <t>226722</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>248383</t>
+          <t>247601</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,6%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>2670</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11852</t>
+          <t>12734</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11284</t>
+          <t>11277</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29242</t>
+          <t>29924</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15981</t>
+          <t>15944</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35263</t>
+          <t>36342</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>134037</t>
+          <t>133155</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>143921</t>
+          <t>143219</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>153438</t>
+          <t>152756</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>171396</t>
+          <t>171403</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>293305</t>
+          <t>292226</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>312587</t>
+          <t>312624</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,15%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>5738</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6240</t>
+          <t>6264</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>19631</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7668</t>
+          <t>7598</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21895</t>
+          <t>22051</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>98439</t>
+          <t>98633</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>115728</t>
+          <t>116219</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>129610</t>
+          <t>129586</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>218326</t>
+          <t>218170</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>232553</t>
+          <t>232623</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,84%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4169</t>
+          <t>4161</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15536</t>
+          <t>15703</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11869</t>
+          <t>12299</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29177</t>
+          <t>29545</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19048</t>
+          <t>19362</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41739</t>
+          <t>40457</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>121681</t>
+          <t>121514</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>133048</t>
+          <t>133056</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>179600</t>
+          <t>179232</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>196908</t>
+          <t>196478</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>304256</t>
+          <t>305538</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>326947</t>
+          <t>326633</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,4%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19727</t>
+          <t>19840</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40061</t>
+          <t>39127</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50678</t>
+          <t>50278</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>82380</t>
+          <t>82118</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>75512</t>
+          <t>74520</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>113593</t>
+          <t>111553</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>462405</t>
+          <t>463339</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>482739</t>
+          <t>482626</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>594462</t>
+          <t>594724</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>626164</t>
+          <t>626564</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1065715</t>
+          <t>1067755</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1103796</t>
+          <t>1104788</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,68%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar el baño o ducha en 2012</t>
+          <t>Población según si es capaz de usar el baño o ducha en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5115</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16868</t>
+          <t>18215</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22583</t>
+          <t>23196</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44165</t>
+          <t>42887</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30313</t>
+          <t>32288</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55212</t>
+          <t>55550</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,13%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>122679</t>
+          <t>121332</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>134432</t>
+          <t>134422</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>122622</t>
+          <t>123900</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>144204</t>
+          <t>143591</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>251122</t>
+          <t>250784</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>276021</t>
+          <t>274046</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>89,46%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13745</t>
+          <t>15055</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32833</t>
+          <t>33466</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41873</t>
+          <t>41053</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65562</t>
+          <t>67367</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>61284</t>
+          <t>61739</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>93650</t>
+          <t>92814</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,8%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>122045</t>
+          <t>121412</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>141133</t>
+          <t>139823</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>125858</t>
+          <t>124053</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>149547</t>
+          <t>150367</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>252648</t>
+          <t>253484</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>285014</t>
+          <t>284559</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,17%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4482</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20564</t>
+          <t>19696</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27030</t>
+          <t>27011</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49420</t>
+          <t>48521</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34484</t>
+          <t>35654</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61829</t>
+          <t>62262</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83034</t>
+          <t>83902</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>99116</t>
+          <t>99119</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>91599</t>
+          <t>92498</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>113989</t>
+          <t>114008</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>182788</t>
+          <t>182355</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>210133</t>
+          <t>208963</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,42%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10141</t>
+          <t>10045</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28685</t>
+          <t>27316</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29170</t>
+          <t>29575</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53176</t>
+          <t>54603</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45075</t>
+          <t>44320</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>76076</t>
+          <t>72376</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>17,85%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>132928</t>
+          <t>134297</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>151472</t>
+          <t>151568</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>190574</t>
+          <t>189147</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>214580</t>
+          <t>214175</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>329287</t>
+          <t>332987</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>360288</t>
+          <t>361043</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>89,07%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46769</t>
+          <t>44951</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>80660</t>
+          <t>77478</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>141120</t>
+          <t>141800</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>187453</t>
+          <t>188729</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>199473</t>
+          <t>197047</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>253902</t>
+          <t>255925</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>478977</t>
+          <t>482159</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>512868</t>
+          <t>514686</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>555522</t>
+          <t>554246</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>601855</t>
+          <t>601175</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1048710</t>
+          <t>1046687</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1103139</t>
+          <t>1105565</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,87%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar el baño o ducha en 2016</t>
+          <t>Población según si es capaz de usar el baño o ducha en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9245</t>
+          <t>9198</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24385</t>
+          <t>23075</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19331</t>
+          <t>18718</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40306</t>
+          <t>40285</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29964</t>
+          <t>30586</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55596</t>
+          <t>56128</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>112349</t>
+          <t>113659</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>127489</t>
+          <t>127536</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>133085</t>
+          <t>133106</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>154060</t>
+          <t>154673</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>254529</t>
+          <t>253997</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>280161</t>
+          <t>279539</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,14%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6072</t>
+          <t>6869</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18516</t>
+          <t>19026</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15770</t>
+          <t>14762</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37027</t>
+          <t>36772</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24872</t>
+          <t>24250</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49258</t>
+          <t>49946</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,0%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>146425</t>
+          <t>145915</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>158869</t>
+          <t>158072</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>182136</t>
+          <t>182391</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>203393</t>
+          <t>204401</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>334846</t>
+          <t>334158</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>359232</t>
+          <t>359854</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,69%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5128</t>
+          <t>4760</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17152</t>
+          <t>17276</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13270</t>
+          <t>12540</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31640</t>
+          <t>31641</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21570</t>
+          <t>21485</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43929</t>
+          <t>44099</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>97883</t>
+          <t>97759</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>109907</t>
+          <t>110275</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>110956</t>
+          <t>110955</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>129326</t>
+          <t>130056</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>213702</t>
+          <t>213532</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>236061</t>
+          <t>236146</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,66%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5446</t>
+          <t>5579</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18959</t>
+          <t>20011</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18856</t>
+          <t>18331</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41744</t>
+          <t>40772</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28029</t>
+          <t>28560</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53927</t>
+          <t>54850</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>155659</t>
+          <t>154607</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>169172</t>
+          <t>169039</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>201037</t>
+          <t>202009</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>223925</t>
+          <t>224450</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>363473</t>
+          <t>362550</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>389371</t>
+          <t>388840</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,16%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37005</t>
+          <t>35881</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60470</t>
+          <t>60862</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>80874</t>
+          <t>84091</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>123926</t>
+          <t>126267</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>127193</t>
+          <t>126324</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>178156</t>
+          <t>174546</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,75%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>530858</t>
+          <t>530466</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>554323</t>
+          <t>555447</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>654005</t>
+          <t>651664</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>697057</t>
+          <t>693840</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1191103</t>
+          <t>1194713</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1242066</t>
+          <t>1242935</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,77%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar el baño o ducha en 2023</t>
+          <t>Población según si es capaz de usar el baño o ducha en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12494</t>
+          <t>12137</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24482</t>
+          <t>25329</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26455</t>
+          <t>26766</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39487</t>
+          <t>39753</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42271</t>
+          <t>42868</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59988</t>
+          <t>61687</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,85%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>123601</t>
+          <t>122754</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>135589</t>
+          <t>135946</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>139676</t>
+          <t>139410</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>152708</t>
+          <t>152397</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>267258</t>
+          <t>265559</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>284975</t>
+          <t>284378</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>86,9%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9221</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20673</t>
+          <t>22061</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28656</t>
+          <t>29091</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45093</t>
+          <t>45529</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42586</t>
+          <t>41878</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61637</t>
+          <t>61998</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,38%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>139441</t>
+          <t>138053</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>150893</t>
+          <t>150248</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>173302</t>
+          <t>172866</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>189739</t>
+          <t>189304</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>316872</t>
+          <t>316511</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>335923</t>
+          <t>336631</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,94%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3107</t>
+          <t>3269</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13222</t>
+          <t>13612</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4724</t>
+          <t>5189</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51858</t>
+          <t>49550</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6913</t>
+          <t>9198</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48906</t>
+          <t>49746</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>123730</t>
+          <t>123340</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>133845</t>
+          <t>133683</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>308398</t>
+          <t>310706</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>355532</t>
+          <t>355067</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>448303</t>
+          <t>447463</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>490296</t>
+          <t>488011</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5624</t>
+          <t>5644</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15709</t>
+          <t>16130</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24531</t>
+          <t>23773</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40330</t>
+          <t>40704</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31884</t>
+          <t>31691</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51036</t>
+          <t>51344</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>189320</t>
+          <t>188899</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>199405</t>
+          <t>199385</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>234693</t>
+          <t>234319</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>250492</t>
+          <t>251250</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>429016</t>
+          <t>428708</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>448168</t>
+          <t>448361</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,4%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38817</t>
+          <t>39462</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61917</t>
+          <t>61756</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>65214</t>
+          <t>68918</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>155659</t>
+          <t>156864</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>114521</t>
+          <t>110236</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>201090</t>
+          <t>201182</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>588261</t>
+          <t>588422</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>611361</t>
+          <t>610716</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>877179</t>
+          <t>875974</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>967624</t>
+          <t>963920</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1481926</t>
+          <t>1481834</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1568495</t>
+          <t>1572780</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,45%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5411-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5411-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>6499</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18658</t>
+          <t>18598</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7672</t>
+          <t>7786</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23685</t>
+          <t>23310</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16923</t>
+          <t>17203</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37802</t>
+          <t>37022</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,0%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>96331</t>
+          <t>96391</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>108560</t>
+          <t>108490</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>125850</t>
+          <t>126225</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>141863</t>
+          <t>141749</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>226722</t>
+          <t>227502</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>247601</t>
+          <t>247321</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,5%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12734</t>
+          <t>11522</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11277</t>
+          <t>11149</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29924</t>
+          <t>29551</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15944</t>
+          <t>16574</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36342</t>
+          <t>37195</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>133155</t>
+          <t>134367</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>143219</t>
+          <t>143827</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>152756</t>
+          <t>153129</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>171403</t>
+          <t>171531</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>292226</t>
+          <t>291373</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>312624</t>
+          <t>311994</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,96%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5738</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6264</t>
+          <t>6498</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19631</t>
+          <t>20023</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7598</t>
+          <t>7607</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22051</t>
+          <t>23318</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>98633</t>
+          <t>98034</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>116219</t>
+          <t>115827</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>129586</t>
+          <t>129352</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>218170</t>
+          <t>216903</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>232623</t>
+          <t>232614</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4161</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15703</t>
+          <t>15852</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12299</t>
+          <t>12180</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29545</t>
+          <t>29945</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19362</t>
+          <t>18983</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40457</t>
+          <t>38966</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>121514</t>
+          <t>121365</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>133056</t>
+          <t>133031</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>179232</t>
+          <t>178832</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>196478</t>
+          <t>196597</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>305538</t>
+          <t>307029</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>326633</t>
+          <t>327012</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,51%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19840</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39127</t>
+          <t>39294</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50278</t>
+          <t>49473</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>82118</t>
+          <t>82329</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>74520</t>
+          <t>73744</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>111553</t>
+          <t>110795</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>463339</t>
+          <t>463172</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>482626</t>
+          <t>481695</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>594724</t>
+          <t>594513</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>626564</t>
+          <t>627369</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1067755</t>
+          <t>1068513</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1104788</t>
+          <t>1105564</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,75%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>5040</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18215</t>
+          <t>17594</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23196</t>
+          <t>22697</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42887</t>
+          <t>43247</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32288</t>
+          <t>31650</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55550</t>
+          <t>56244</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,36%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>121332</t>
+          <t>121953</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>134422</t>
+          <t>134507</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>123900</t>
+          <t>123540</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>143591</t>
+          <t>144090</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>250784</t>
+          <t>250090</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>274046</t>
+          <t>274684</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,67%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15055</t>
+          <t>14372</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33466</t>
+          <t>33925</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41053</t>
+          <t>42170</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67367</t>
+          <t>67770</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>61739</t>
+          <t>62538</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>92814</t>
+          <t>94853</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>27,39%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>121412</t>
+          <t>120953</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>139823</t>
+          <t>140506</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>124053</t>
+          <t>123650</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>150367</t>
+          <t>149250</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>253484</t>
+          <t>251445</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>284559</t>
+          <t>283760</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>81,94%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4479</t>
+          <t>4609</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19696</t>
+          <t>19951</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27011</t>
+          <t>26647</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48521</t>
+          <t>48416</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35654</t>
+          <t>34570</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62262</t>
+          <t>59866</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>24,47%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83902</t>
+          <t>83647</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>99119</t>
+          <t>98989</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92498</t>
+          <t>92603</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>114008</t>
+          <t>114372</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>182355</t>
+          <t>184751</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>208963</t>
+          <t>210047</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,87%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10045</t>
+          <t>9968</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27316</t>
+          <t>28180</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29575</t>
+          <t>29636</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54603</t>
+          <t>53369</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44320</t>
+          <t>44349</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>72376</t>
+          <t>73710</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>134297</t>
+          <t>133433</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>151568</t>
+          <t>151645</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>189147</t>
+          <t>190381</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>214175</t>
+          <t>214114</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>332987</t>
+          <t>331653</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>361043</t>
+          <t>361014</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,06%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44951</t>
+          <t>46468</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>77478</t>
+          <t>78774</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>141800</t>
+          <t>140867</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>188729</t>
+          <t>186359</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>197047</t>
+          <t>196079</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>255925</t>
+          <t>251238</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>482159</t>
+          <t>480863</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>514686</t>
+          <t>513169</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>554246</t>
+          <t>556616</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>601175</t>
+          <t>602108</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1046687</t>
+          <t>1051374</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1105565</t>
+          <t>1106533</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,95%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9198</t>
+          <t>8679</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23075</t>
+          <t>22330</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18718</t>
+          <t>17962</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40285</t>
+          <t>38512</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30586</t>
+          <t>31260</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56128</t>
+          <t>56433</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,2%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>113659</t>
+          <t>114404</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>127536</t>
+          <t>128055</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>133106</t>
+          <t>134879</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>154673</t>
+          <t>155429</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>253997</t>
+          <t>253692</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>279539</t>
+          <t>278865</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>89,92%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6869</t>
+          <t>6932</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19026</t>
+          <t>20810</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14762</t>
+          <t>15128</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36772</t>
+          <t>36692</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24250</t>
+          <t>24322</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49946</t>
+          <t>49793</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>145915</t>
+          <t>144131</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>158072</t>
+          <t>158009</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>182391</t>
+          <t>182471</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>204401</t>
+          <t>204035</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>334158</t>
+          <t>334311</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>359854</t>
+          <t>359782</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,67%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4760</t>
+          <t>4815</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17276</t>
+          <t>17258</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12540</t>
+          <t>13428</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31641</t>
+          <t>32871</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21485</t>
+          <t>22077</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44099</t>
+          <t>44438</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,25%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>97759</t>
+          <t>97777</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>110275</t>
+          <t>110220</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>110955</t>
+          <t>109725</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>130056</t>
+          <t>129168</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>213532</t>
+          <t>213193</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>236146</t>
+          <t>235554</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,43%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5579</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20011</t>
+          <t>18563</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18331</t>
+          <t>18845</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40772</t>
+          <t>40949</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28560</t>
+          <t>29239</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54850</t>
+          <t>56215</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,47%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>154607</t>
+          <t>156055</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>169039</t>
+          <t>168542</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>202009</t>
+          <t>201832</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>224450</t>
+          <t>223936</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>362550</t>
+          <t>361185</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>388840</t>
+          <t>388161</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,0%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35881</t>
+          <t>36871</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60862</t>
+          <t>60684</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>84091</t>
+          <t>83197</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>126267</t>
+          <t>124541</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>126324</t>
+          <t>127556</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>174546</t>
+          <t>176448</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>530466</t>
+          <t>530644</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>555447</t>
+          <t>554457</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>651664</t>
+          <t>653390</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>693840</t>
+          <t>694734</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1194713</t>
+          <t>1192811</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1242935</t>
+          <t>1241703</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,68%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>17986</t>
+          <t>19057</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12137</t>
+          <t>13461</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25329</t>
+          <t>26452</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>32618</t>
+          <t>34048</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26766</t>
+          <t>27788</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39753</t>
+          <t>41602</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>50605</t>
+          <t>53104</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42868</t>
+          <t>44798</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61687</t>
+          <t>63981</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,06%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>130097</t>
+          <t>144257</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>122754</t>
+          <t>136862</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>135946</t>
+          <t>149853</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>146545</t>
+          <t>156981</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>139410</t>
+          <t>149427</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>152397</t>
+          <t>163241</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>276641</t>
+          <t>301239</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>265559</t>
+          <t>290362</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>284378</t>
+          <t>309545</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>87,36%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14808</t>
+          <t>15910</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9866</t>
+          <t>10417</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22061</t>
+          <t>23670</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36362</t>
+          <t>39477</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29091</t>
+          <t>31584</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45529</t>
+          <t>48726</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>51170</t>
+          <t>55387</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41878</t>
+          <t>44927</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61998</t>
+          <t>66928</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>145306</t>
+          <t>162294</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>138053</t>
+          <t>154534</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>150248</t>
+          <t>167787</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>182033</t>
+          <t>202185</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>172866</t>
+          <t>192936</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>189304</t>
+          <t>210078</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>327339</t>
+          <t>364479</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>316511</t>
+          <t>352938</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>336631</t>
+          <t>374939</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>89,3%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>218395</t>
+          <t>241662</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>218395</t>
+          <t>241662</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>218395</t>
+          <t>241662</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>378509</t>
+          <t>419866</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>378509</t>
+          <t>419866</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>378509</t>
+          <t>419866</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7057</t>
+          <t>7801</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>3681</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13612</t>
+          <t>14362</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20131</t>
+          <t>22067</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>15666</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49550</t>
+          <t>30089</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>27189</t>
+          <t>29868</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9198</t>
+          <t>22030</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49746</t>
+          <t>39275</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>129895</t>
+          <t>151984</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>123340</t>
+          <t>145423</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>133683</t>
+          <t>156104</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>340125</t>
+          <t>152842</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>310706</t>
+          <t>144820</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>355067</t>
+          <t>159243</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>470020</t>
+          <t>304826</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>447463</t>
+          <t>295419</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>488011</t>
+          <t>312664</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>93,42%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>497209</t>
+          <t>334694</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>497209</t>
+          <t>334694</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>497209</t>
+          <t>334694</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9799</t>
+          <t>10212</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5644</t>
+          <t>6125</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16130</t>
+          <t>15631</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31160</t>
+          <t>34263</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23773</t>
+          <t>26332</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40704</t>
+          <t>43347</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>40960</t>
+          <t>44474</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31691</t>
+          <t>34901</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51344</t>
+          <t>55778</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>195230</t>
+          <t>204877</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>188899</t>
+          <t>199458</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>199385</t>
+          <t>208964</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>243863</t>
+          <t>260456</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>234319</t>
+          <t>251372</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>251250</t>
+          <t>268387</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>439092</t>
+          <t>465333</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>428708</t>
+          <t>454029</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>448361</t>
+          <t>474906</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,15%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>205029</t>
+          <t>215089</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>205029</t>
+          <t>215089</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>205029</t>
+          <t>215089</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>275023</t>
+          <t>294719</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>275023</t>
+          <t>294719</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>275023</t>
+          <t>294719</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>480052</t>
+          <t>509807</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>480052</t>
+          <t>509807</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>480052</t>
+          <t>509807</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>49651</t>
+          <t>52979</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39462</t>
+          <t>42471</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61756</t>
+          <t>67575</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>120272</t>
+          <t>129855</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>68918</t>
+          <t>115502</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>156864</t>
+          <t>146572</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>169923</t>
+          <t>182834</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>110236</t>
+          <t>164800</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>201182</t>
+          <t>204185</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>600527</t>
+          <t>663412</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>588422</t>
+          <t>648816</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>610716</t>
+          <t>673920</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>912566</t>
+          <t>772464</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>875974</t>
+          <t>755747</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>963920</t>
+          <t>786817</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1513093</t>
+          <t>1435876</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1481834</t>
+          <t>1414525</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1572780</t>
+          <t>1453910</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>89,82%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1032838</t>
+          <t>902319</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1032838</t>
+          <t>902319</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1032838</t>
+          <t>902319</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1683016</t>
+          <t>1618710</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1683016</t>
+          <t>1618710</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1683016</t>
+          <t>1618710</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
